--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45048</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>44546</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>46030</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45483</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45205</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45756</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>45772</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>45766</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45209</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45335</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>45264</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>44979</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>45077</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45539</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>46078</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>46195</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>45091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>43980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45418</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44566</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>44602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44788</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44468</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>44459</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>44557</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44608</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44879</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44480</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44523</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44770</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>44558</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44840</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44729</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44515</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44753</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44600</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44858</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44607</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44496</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44473</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44473</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44539</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44760</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44469</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44776</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44496</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44557</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44572</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44525</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44825</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44854</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44502</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44606</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44616</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44477</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44706</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44662</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44678</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44648</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45597</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44727</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45386</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>45618</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45567</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45567</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45735</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45642</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44616</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45394</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45358</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45238</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45113</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45142</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44595</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45328</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45635</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45250</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45772</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45267</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>44943</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45363</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44887</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45558</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44909</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44936</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>45735</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45483</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45161</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45761</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44851</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45328</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45328</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45200</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45308</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44859</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45187</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>44981</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45208</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>44971</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44678</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45531</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45524</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45245</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44903</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45221</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44846</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45446</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44956</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45203</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>44642</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>44642</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45637</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44602</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45587</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45587</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45610</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44566</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44577</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45167</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44727</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>45069</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45590</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45267</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45667</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>45203</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45562</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45217</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45328</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45853</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45245</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45519</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45324</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44722</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45670</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45264</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45583</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44853</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44853</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45726</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45957</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45576</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45678</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45758</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44722</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45853</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45889</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45785</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>45966</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>44984</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44470</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45509</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>46139</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45175</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45567</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>45873</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45905</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45566</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>45642</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45841</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44823</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45208</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>45807</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45194</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45512</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45758</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45841</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45785</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>45936</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45812</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45056</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45664</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45509</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>45876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>45827</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45917</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44966</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45919</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45274</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45229</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44461</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45149</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44931</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45684</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45044</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45239</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45320</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45261</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44993</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44882</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45112</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>46098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45667</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45713</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45946</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45105</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45105</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45043</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45372</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45400</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45221</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44970</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45272</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45369</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44998</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44831</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45957</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45957</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45957</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45957</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44608</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45965</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45965</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45966</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45967</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45446</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45357</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45971</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45971</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44642</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45756</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45971</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45972</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45975</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>45975</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45496</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45981</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45264</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45981</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44985</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45021</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45718</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44557</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45278</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>44470</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45986</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45987</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45987</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45986</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44539</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45989</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45687</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>44928</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45607</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45993</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>45993</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>46160</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45608</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45558</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>46162</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45622</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44970</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45200</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>45106</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>44686</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44942</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45414</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45995</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45274</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44797</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46003</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45589</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>46001</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>46001</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45701</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>46167</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>46006</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46006</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46007</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>45505</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45267</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45204</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45264</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45007</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45154</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45308</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45443</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45106</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>45302</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>44652</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45072</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45271</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45769</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
         <v>46030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>46030</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45204</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>45475</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46034</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>46034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45474</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>46034</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45972</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>46037</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44994</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>46038</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>46038</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>46038</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46038</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>46042</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46042</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>46042</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>46045</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46044</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>46172</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>46045</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>46045</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>46101</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45945</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45509</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>46049</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45308</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>46050</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45105</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45105</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45631</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>45012</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>46177</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>46057</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>46057</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45078</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>46062</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>46062</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>46064</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45357</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>46064</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45069</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>46066</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>45763</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>44846</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45517</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>46073</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>46073</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45713</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>46073</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>46073</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>46073</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>46073</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>46073</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46182</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44526</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46183</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>46078</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45371</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45238</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>46080</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45160</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>46079</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>46184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>46185</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>45219</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>46080</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45223</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45224</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>46188</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>46086</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>46188</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46188</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>46188</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>46188</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>46189</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44501</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>46190</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>46092</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>46093</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>46190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45114</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45674</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45674</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46190</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>46193</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>46191</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>46191</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46099</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>46191</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>46191</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>46191</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>46191</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>46099</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>46195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46195</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>46195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45563</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>46195</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>46195</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         <v>46195</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36063,7 +36063,7 @@
         <v>44587</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>46195</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45243</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45243</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45174</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46195</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>44559</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46105</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>46105</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45278</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>45200</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>46101</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44820</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37032,7 +37032,7 @@
         <v>45170</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45258</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>46093</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45372</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46127</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45645</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>46127</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45406</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>46127</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45275</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45596</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45194</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44729</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>44949</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46204</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>45912</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45270</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>44890</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45105</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45674</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45009</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45688</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45554</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45721</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45188</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45547</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45245</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44949</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45243</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>46251</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45558</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>44553</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>44553</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45701</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>46206</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45924</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45393</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>46206</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45713</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>46251</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45173</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46206</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>46206</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45343</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45343</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45188</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45167</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45566</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>44805</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>44698</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>46254</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>46105</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>46258</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44936</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45044</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45278</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45607</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45728</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45279</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>46265</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44699</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>46265</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45197</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45197</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>46265</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>46267</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45146</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45271</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45265</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>44998</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>44998</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45036</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45037</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46268</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45777</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45589</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>46230</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>46230</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>46230</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45468</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45428</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45547</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46276</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>46279</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>45243</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>46279</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45445</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45790</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46269</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45723</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>46281</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45561</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45792</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46238</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46238</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45796</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46244</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>46283</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45674</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>46244</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45803</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45800</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45439</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45750</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45180</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45670</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>45608</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45649</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45819</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45820</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45825</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45825</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45827</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45826</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45832</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45832</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45833</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45805</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45659</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45841</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45841</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45841</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45845</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45586</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45604</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45853</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>45748</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45802</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45873</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45873</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45876</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>44379</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45194</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45427</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45418</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>45117</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>44991</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45119</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45425</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44519</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45440</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45583</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44519</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>45105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45122</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>44479</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>46010</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>46018</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>46052</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45048</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45205</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>46030</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45483</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44546</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44879</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45422</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45712</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46164</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44508</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>46078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45772</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46195</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45264</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45335</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>46286</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>46287</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45766</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45539</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>43980</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45418</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44566</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44788</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44729</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44753</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44473</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44539</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44760</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44776</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44496</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44557</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44572</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44757</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44854</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44502</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44477</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44706</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44678</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44648</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45267</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44823</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45324</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45221</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>45401</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45406</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45343</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45037</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45363</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45243</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44853</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44853</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45558</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45393</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45243</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45446</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44494</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44949</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45271</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44966</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46030</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46030</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45792</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45170</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45674</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44602</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>46034</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>44470</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45853</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45576</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45512</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44984</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>46038</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>46038</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45562</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45091</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>46045</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>46045</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>46045</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>46045</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45758</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45807</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45194</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45357</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45670</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45800</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45439</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44557</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44949</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>46057</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>46057</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45915</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>46062</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46064</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44998</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44998</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>46064</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44595</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46066</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45919</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44553</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44553</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45803</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>45217</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45567</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>46073</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>46073</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45261</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46073</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46073</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46073</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45197</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45197</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45567</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>46080</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45558</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>46086</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45180</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45587</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46092</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46093</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44470</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45670</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46099</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44956</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45772</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45959</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>46105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45957</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45957</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45270</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46101</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44931</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46127</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44942</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45967</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44526</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45044</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45971</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44722</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45637</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45012</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46127</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45972</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45414</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45166</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45674</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45981</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45986</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45674</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45987</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45785</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45649</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45989</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45873</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45957</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45841</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45905</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45993</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45189</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45876</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45726</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44722</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45758</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46001</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45219</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46139</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46006</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45819</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>46006</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44473</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45509</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44846</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45036</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45812</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44727</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45224</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45936</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45966</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45308</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45200</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45912</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45154</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45267</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45509</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45567</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45761</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45519</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45889</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45735</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45825</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45826</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45827</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45446</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45664</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45072</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45735</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44869</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45659</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45805</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45208</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45832</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45208</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45833</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45718</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45496</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45021</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>46162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45841</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45841</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45845</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45245</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45604</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45853</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44887</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45748</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>46172</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44805</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44936</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45945</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45972</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45589</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45019</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45029</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45106</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44970</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45802</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45114</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>46177</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45124</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45769</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45553</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45264</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45264</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45873</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45162</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45250</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44559</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45517</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46189</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46188</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46191</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46191</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45873</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46191</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46191</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46190</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46190</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46195</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46195</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>46195</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45876</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>46195</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46193</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45713</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44642</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44642</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45160</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45631</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45721</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45608</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44566</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45635</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45328</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45328</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45371</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45684</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46204</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46251</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45372</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45554</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46206</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44608</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46251</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45642</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>46105</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45607</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>44699</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44698</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46258</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45093</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45173</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45188</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45769</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45274</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44678</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45194</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45688</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45239</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46265</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44851</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45278</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44729</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45243</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>44686</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>46265</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>46265</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45728</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>44909</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45328</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45265</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45320</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46268</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44859</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45763</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>46230</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>46230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46230</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45278</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45279</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44820</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45509</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45610</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46269</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45701</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>44936</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>46281</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46238</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45308</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45308</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46238</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44993</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45590</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45394</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46283</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>44652</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46283</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>46287</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>46288</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44840</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>44825</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46282</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>46288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46288</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45443</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44985</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44928</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45566</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44970</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45971</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45607</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46288</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45200</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>46007</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>46098</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45622</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45187</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45713</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45203</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46244</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>46080</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>45036</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>44501</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45267</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44846</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45043</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44616</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45221</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>44971</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45474</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45642</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>44903</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44642</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44577</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45106</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45274</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45369</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45386</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45357</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45563</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45400</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45642</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45078</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45372</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45009</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45328</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45105</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>45105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45105</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44727</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45678</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45162</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>44998</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45105</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45200</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45056</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45371</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45596</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45547</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44882</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45278</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45505</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45167</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45713</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45483</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45271</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45674</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45667</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45204</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45597</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45229</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45358</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45684</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45146</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45264</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45667</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45160</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45777</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45589</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45428</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>45445</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45547</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>45468</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45243</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45790</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45561</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45723</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>44379</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45194</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45427</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>45418</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45117</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>44991</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45119</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45425</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>44519</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45440</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45583</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>44519</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45122</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>44479</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46010</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>46018</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46052</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45048</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45205</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>46030</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45483</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44546</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44879</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45422</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45712</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46164</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45091</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44508</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>46078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45772</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>45841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>46188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46195</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>46268</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45264</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45335</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>46286</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>46287</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45766</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>45539</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>43980</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45418</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44566</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44788</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44468</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44480</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44729</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44753</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44600</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44473</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44539</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44760</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44776</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>44848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44496</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44557</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44572</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44525</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44757</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44854</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44502</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44606</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44477</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44706</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44678</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44648</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45267</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44823</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45174</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45324</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45221</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>45401</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45406</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45343</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45037</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45363</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45243</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>44853</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>44853</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45756</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45558</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45393</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45315</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45243</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45446</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45796</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>44494</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44949</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45271</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>45734</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44966</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46030</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>46030</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>45792</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45170</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11208,7 +11208,7 @@
         <v>45674</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44602</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>46034</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>44470</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>45785</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45853</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45576</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45512</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>44984</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45475</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>46038</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>46037</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>46038</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>46038</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>46038</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45562</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45091</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>46045</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45113</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>46045</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>46045</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>46045</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45758</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45807</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45194</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>46050</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45357</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>45670</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45800</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45439</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>44557</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44949</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>44943</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45558</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>46057</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>46057</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>46062</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45915</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45524</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>46062</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>46064</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44998</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>44998</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>46064</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>44595</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46066</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45919</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45007</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44553</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>44553</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45803</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>45217</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44890</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45567</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>46073</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>46073</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45261</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>46073</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46073</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46073</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45197</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45197</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45567</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>46079</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>46080</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45558</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>46086</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45180</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45587</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>46092</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46093</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44470</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45670</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45142</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>46099</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45946</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44956</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45772</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45093</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45959</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>46105</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45957</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45957</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45270</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>46101</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44931</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45965</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>46127</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44929</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44942</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45967</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44526</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45044</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45971</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44722</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45637</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45012</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46127</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45972</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45414</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45166</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45674</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45981</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45986</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45701</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45674</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45987</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45785</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45649</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45989</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45873</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45957</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45841</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45905</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45993</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45189</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45876</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45726</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44722</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45758</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46001</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45219</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46139</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46006</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45819</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>46006</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44473</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45509</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>44846</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45036</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45812</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44727</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45224</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45936</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45966</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45308</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45200</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45912</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45154</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45267</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45509</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45567</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45761</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45519</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45889</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45735</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45825</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45826</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45827</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45446</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45664</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45072</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45735</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>45069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44869</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45659</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45805</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44831</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45208</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45832</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45208</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45833</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45718</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>45496</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45021</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>46162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45841</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45841</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45845</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45245</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45604</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45853</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>44887</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45748</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45149</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>46172</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44805</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44936</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45945</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45972</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45589</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45019</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45029</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45106</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44970</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45802</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45114</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>46177</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45124</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45769</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45553</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45264</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45264</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>46182</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45873</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46184</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45162</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>46185</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45250</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44559</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45517</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46189</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46188</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46188</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46188</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46191</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46191</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>45873</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46191</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46191</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46190</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46190</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46195</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>46195</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>46195</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45876</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>46195</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46193</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46195</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45713</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45188</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44642</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44642</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>45160</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45631</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45721</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>45608</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44566</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45635</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45328</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>46093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45328</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45204</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45371</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45645</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45684</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46204</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46251</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45372</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45554</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46206</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>45044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44608</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46251</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45642</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>46105</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45607</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>44699</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>46254</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>44698</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46258</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45093</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>45173</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45188</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45769</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>45274</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>44678</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35425,7 +35425,7 @@
         <v>45194</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45688</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>45239</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35649,7 +35649,7 @@
         <v>46265</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44851</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45278</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>44729</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45243</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>44686</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>46265</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>46265</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45728</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>44909</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45328</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45265</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45320</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>46267</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46268</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44859</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45763</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>46230</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>46230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46230</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45278</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45279</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46276</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44820</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45509</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45610</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46269</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45701</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45302</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>44936</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45223</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>46281</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46238</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45308</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45308</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46238</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44993</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45590</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45394</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46283</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>44652</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46283</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>46287</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>46288</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>44840</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>44825</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>46282</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>46288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46288</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45443</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44985</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44928</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45566</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>44970</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45971</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45607</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46288</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45200</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>46007</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>46098</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45622</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>45187</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45713</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46244</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45203</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46244</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>46080</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>45036</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>44501</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45267</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44846</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45043</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44616</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45245</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45221</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>44971</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45474</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45642</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>44903</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>44642</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44577</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45106</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45274</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45175</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45369</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45386</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45357</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45563</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45400</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45642</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45078</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45372</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45009</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45328</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>45105</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>45105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45105</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44727</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45678</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45162</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>44998</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45105</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45200</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45056</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45371</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45596</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45547</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44882</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45278</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45505</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45167</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45713</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45687</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45483</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45271</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45674</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45667</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45204</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45597</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45229</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45358</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45684</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45146</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45264</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45667</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45160</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45777</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45589</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45428</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46188,7 +46188,7 @@
         <v>45445</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>45547</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>45468</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45243</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45790</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45561</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45723</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>44379</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45194</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45427</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>45418</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>45117</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>44991</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45119</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45425</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>44519</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45440</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45583</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>44519</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45122</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>44479</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46010</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>46018</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>46052</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45048</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46030</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>44546</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45483</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45205</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44879</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45422</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45712</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46164</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45772</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45766</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45209</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46078</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46286</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46287</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>43980</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45418</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44566</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44788</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44557</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44760</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44848</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44496</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44757</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44502</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44606</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44678</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44648</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44727</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44929</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45386</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45618</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45328</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45684</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45358</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45642</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44869</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45243</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45772</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45238</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45113</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45142</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>44595</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45445</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>46003</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>46001</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>46001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45790</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45250</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45267</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45583</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45769</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45723</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45363</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45308</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44936</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45735</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45853</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45558</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45889</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45785</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45483</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>46029</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45761</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44851</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45328</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45328</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45807</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45758</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45200</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46034</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45308</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46034</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45187</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>46037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46038</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46038</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44859</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>46038</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44981</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46042</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46045</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>46045</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>46049</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45917</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45674</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45800</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>46050</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45439</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44678</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46057</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>46057</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>46062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46064</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46064</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45245</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45524</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45180</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45221</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>44903</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46073</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46073</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46073</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>46073</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46073</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46073</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45670</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45446</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45189</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44956</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46080</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44602</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45203</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45608</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44642</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44642</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46079</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45637</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45959</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45610</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>46086</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45957</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45957</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44577</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45587</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>46092</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44727</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45069</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45590</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45267</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45667</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45203</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>44840</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45649</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45819</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45562</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45217</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45987</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45825</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45328</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45825</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>46101</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45989</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45245</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45324</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44722</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45993</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45191</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45264</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45995</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44494</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46127</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44853</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44853</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45678</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45832</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45832</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45833</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45805</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45659</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>44984</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45509</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45566</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45642</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44823</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45208</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45845</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45519</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45604</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45124</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45056</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45726</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45957</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44473</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45758</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>44966</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45853</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45917</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45966</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45274</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45889</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>46139</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45567</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45873</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45229</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45905</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45748</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45841</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45841</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45149</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45785</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45936</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44931</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45684</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45044</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45239</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45261</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44993</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45509</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45876</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45112</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45667</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45713</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45105</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45105</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45802</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45043</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45372</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45400</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45221</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45873</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45642</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45272</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45369</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45873</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>44831</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44608</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45718</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45446</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45357</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45756</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45496</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45876</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45264</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44985</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45021</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45401</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44557</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45278</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45029</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46167</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44539</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45160</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46172</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44928</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45945</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45576</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>46177</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45622</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44970</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45200</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45106</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44686</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44942</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45414</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>46184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>46185</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>46188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46188</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46188</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45302</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46189</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45589</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>46190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45701</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46190</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>46190</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>46193</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>46191</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46191</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>46191</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>46191</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>46191</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>46191</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45505</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46195</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>46195</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46195</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>46195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46195</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>46195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45264</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46195</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45154</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45443</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45106</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45302</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44652</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45271</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45162</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45162</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46093</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45769</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45475</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45474</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45924</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44994</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>46206</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46206</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>46105</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>46258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45509</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45308</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45105</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45105</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45631</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45012</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>46265</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46265</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>46267</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45357</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45069</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44846</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45517</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45713</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44526</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45371</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46230</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>46230</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>46230</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45223</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45224</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>46276</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>46279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46279</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>46281</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>46238</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>46238</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44501</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45114</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>45674</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45674</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46283</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>45563</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44587</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45243</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45243</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45971</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45174</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44559</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46282</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46283</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45278</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46289</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46288</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46288</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>46288</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46288</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45200</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46288</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>44820</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44825</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45170</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45713</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45258</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45093</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45372</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45645</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>46007</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45406</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46080</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46244</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>46251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>46294</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>46294</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45596</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45194</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>44729</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44949</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45270</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>44890</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>46294</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45105</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45674</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45009</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45688</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45554</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45721</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>46294</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45188</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45547</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45245</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>44949</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46254</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45243</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45558</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>44553</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>44553</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45701</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46297</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46296</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45393</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45173</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45343</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45343</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45167</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45566</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>44805</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44698</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>44936</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45044</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45607</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45279</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>44699</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45197</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45146</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45271</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45265</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44998</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44998</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45036</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45037</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45777</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45589</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45468</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45428</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45547</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44379</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45194</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45427</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45418</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45117</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44991</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45119</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45425</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44519</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45440</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45583</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>44519</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45105</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45122</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>44479</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>46010</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46018</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>46052</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45070</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45119</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45048</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46030</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>44546</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45483</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>45205</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>44879</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>45422</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45070</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45712</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45825</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>46000</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46164</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45772</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45766</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>45209</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45335</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>45264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>46078</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>45841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>46268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46286</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46287</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>45091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>43980</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45418</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>44602</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>44566</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44853</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44788</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44557</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44760</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>44848</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44496</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44557</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44525</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44757</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44502</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44606</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44662</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44678</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44648</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44727</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44929</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45597</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45386</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45618</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45328</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45684</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45567</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>45166</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45735</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>45358</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45642</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44869</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45243</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45772</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45238</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45113</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45142</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>44595</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45445</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>46003</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>45315</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45512</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>46001</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>46001</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>46006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45790</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45853</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>46006</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45250</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>45635</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45267</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>45583</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45769</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45723</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45561</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45363</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45308</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44936</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45735</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44887</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45853</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45558</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45558</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45889</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45785</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45734</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45483</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>46029</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45761</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44851</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>46030</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>46030</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45328</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45328</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45807</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45758</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45553</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45200</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46034</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45308</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>46034</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45187</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>46037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46038</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46038</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44859</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>46038</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>44981</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>45796</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>46042</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46045</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>46045</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46045</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>46049</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>45917</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45674</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>45917</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45800</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>46050</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45439</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44678</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46057</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>46057</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>46062</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46062</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>46064</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46064</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45245</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>46066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45524</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>45180</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45221</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>44903</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46073</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>46073</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>46073</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>46073</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46073</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>46073</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45670</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45446</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45189</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44956</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>46080</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44602</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>45203</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45608</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44642</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44642</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>46079</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45637</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45959</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45610</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>46086</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45957</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45957</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45957</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45957</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>44577</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45587</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>46092</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44566</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>44727</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45069</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45965</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45590</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45267</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45371</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45971</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45971</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>46099</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46099</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45667</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45975</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45975</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>46105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45203</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>44840</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45649</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45981</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45819</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45820</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45562</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45217</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45987</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45987</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45825</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45328</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45825</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>46101</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45989</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45245</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45324</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44722</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45993</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45670</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45191</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45264</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45995</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44494</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46127</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46127</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>44853</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44853</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45678</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45832</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45832</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45833</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45805</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45659</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>44984</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45509</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>45175</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45912</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45566</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45642</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44823</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45208</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45845</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>45519</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45604</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45124</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45056</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45726</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>45957</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44473</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45758</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>44966</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45853</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45917</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45966</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45274</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45889</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>46139</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>45567</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45873</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45229</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45905</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45748</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45841</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45841</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45149</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>45785</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45936</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>44931</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45684</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45044</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45239</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45261</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44993</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45509</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45876</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45827</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45112</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45667</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45713</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45105</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45105</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>45802</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45043</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45372</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45400</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45221</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45873</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>45642</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45272</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45369</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45873</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>44831</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44608</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45718</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45446</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45357</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>44642</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45756</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>46160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>46162</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45763</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45496</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45876</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45264</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44985</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45021</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45401</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44557</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45278</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45029</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46167</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>44539</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45160</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45687</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>46172</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44928</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45945</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45576</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>46177</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45608</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45558</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45622</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44970</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45200</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>45106</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44686</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>46183</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>44942</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>45414</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45274</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>46184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>46185</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>46188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>46188</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>46188</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45302</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46189</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45589</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>46190</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45701</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>46190</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33477,7 +33477,7 @@
         <v>46190</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>46193</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>46191</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46191</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>46191</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>46191</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>46191</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>46191</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45505</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>46195</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>46195</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>46195</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>46195</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>46195</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46195</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>46195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45264</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45007</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46195</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>45154</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45443</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>45106</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45302</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44652</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>45072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45271</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45162</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45162</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>46093</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45769</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35863,7 +35863,7 @@
         <v>46204</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45204</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45475</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45474</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>46206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45924</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>44994</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>46206</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46206</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>46105</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>46258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45509</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45308</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45105</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45105</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45631</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>45012</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>46265</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46265</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45078</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>46267</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45357</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45069</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44846</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45517</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45713</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38073,7 +38073,7 @@
         <v>44526</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45371</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46230</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45219</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>46230</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>46230</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>45223</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45224</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>46276</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>46279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>46279</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>46281</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>46238</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>46238</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44501</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45114</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>45674</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45674</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>46283</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39709,7 +39709,7 @@
         <v>45563</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39782,7 +39782,7 @@
         <v>44587</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45243</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45243</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45971</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45174</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>44559</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46282</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46283</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46286</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45278</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46289</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>46288</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46288</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>46288</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46288</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45200</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46288</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46288</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>44820</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44825</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45170</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45713</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45258</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45093</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45372</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45645</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>46007</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45406</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46080</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46244</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>46251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>46294</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>46294</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45596</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45194</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>44729</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44949</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45270</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>44890</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>46294</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43044,7 +43044,7 @@
         <v>45105</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45674</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45009</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45688</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45554</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45721</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>46294</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>45188</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45547</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45245</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>44949</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>46254</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43993,7 +43993,7 @@
         <v>45243</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>45558</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>44553</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>44553</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45701</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46297</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>46296</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45393</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45173</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45343</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45343</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45188</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45167</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45566</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>44805</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44698</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>44936</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>45044</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45278</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45607</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45279</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>44699</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45197</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45146</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45271</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45265</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44998</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>44998</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45036</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45037</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45777</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45589</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45468</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45428</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45547</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44379</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45194</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45427</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45418</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45117</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44991</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45119</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45425</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44519</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45440</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45583</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>44519</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47517,7 +47517,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47590,7 +47590,7 @@
         <v>45105</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45122</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47736,7 +47736,7 @@
         <v>44479</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>46010</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46018</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46050</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>46052</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45483</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46030</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44508</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45772</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45335</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>46195</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46286</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46287</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>43980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45418</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>44629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44788</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44557</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44848</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44502</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44616</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44539</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44760</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44776</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44496</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44662</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44678</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44648</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45406</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45343</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45343</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45078</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45372</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45363</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45208</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45763</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45267</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44823</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45105</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45105</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44727</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45221</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45162</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45021</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44998</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44853</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44853</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45756</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45393</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45243</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45200</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45315</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45245</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45056</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45401</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44539</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45371</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45547</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>44494</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44882</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44949</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45278</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45505</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45271</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45149</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44966</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45785</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44805</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45853</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45853</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45576</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45618</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45512</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>44936</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45713</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45687</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45583</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45589</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45483</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45271</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45019</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45674</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44602</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45894</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44981</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45667</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45204</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45758</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44984</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45597</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45531</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45229</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45475</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45194</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45358</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45029</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45146</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45264</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45562</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45667</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45124</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45769</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45777</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45553</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45264</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45264</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45589</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45428</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45357</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45670</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45445</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44949</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45250</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45547</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45917</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44559</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45468</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45517</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45524</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45243</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44998</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44998</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44595</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45790</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>44553</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45217</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45561</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44890</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45567</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44642</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45723</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45261</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45567</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45558</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45796</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45631</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45721</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45792</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>44566</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45558</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45328</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45328</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45674</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45204</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45371</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45587</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45587</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45800</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45439</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45645</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45684</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45142</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45803</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45372</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45554</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44956</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45044</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44608</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45608</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45772</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45180</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45670</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45607</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45946</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44699</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45649</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45270</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45819</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44698</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45820</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44931</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45173</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45826</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44942</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44526</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45832</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44722</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45637</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45012</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45769</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45957</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45957</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45957</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45659</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45805</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45274</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45833</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44678</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45258</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45194</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45414</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45688</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45965</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45965</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45674</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45967</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44851</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45278</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45841</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45701</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45238</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45841</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45841</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45674</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45845</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44729</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45243</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>44686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45586</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45604</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45853</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45748</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45328</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45265</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45272</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45320</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45219</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45161</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44797</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45802</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>44859</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44846</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45873</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45191</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44727</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45224</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45873</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45876</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45278</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45981</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45200</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44820</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45154</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45267</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45509</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45509</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45566</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>46099</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>46099</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45735</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45986</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45986</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45701</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45302</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44936</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45446</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>46105</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45072</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45308</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45308</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45987</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45735</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45987</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45590</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45989</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45394</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45069</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44869</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>46101</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45993</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>46127</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44652</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>46001</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>46001</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44840</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45443</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>44985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>44928</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46003</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45566</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44970</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45607</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45200</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45187</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45873</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45957</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45905</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45308</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45036</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45734</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45876</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44501</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>44846</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44616</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45758</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>46030</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45245</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46139</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45245</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45221</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44971</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>46034</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45509</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45642</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44903</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44642</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45106</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45812</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45966</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46037</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>46038</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>46038</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46038</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46042</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46042</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45112</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45841</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45912</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>46045</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45567</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45386</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45519</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45357</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45563</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45917</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>46045</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46045</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45400</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>46050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45827</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45664</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46057</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>46057</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>46062</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>46062</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>46064</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46064</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46066</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46073</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46073</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46073</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46073</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>44831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46073</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46079</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>46080</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45718</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46086</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46160</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>46092</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46167</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46167</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46167</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46167</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46172</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45945</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45972</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46183</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46182</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>46184</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46185</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46189</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46188</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>46188</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>46188</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46191</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46191</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46190</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46191</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>46191</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46191</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>46195</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46195</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46195</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>46195</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46193</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>46195</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46195</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>46195</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46206</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>46206</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46206</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45924</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46105</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46265</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46265</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46265</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45728</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>46267</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46268</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>46230</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46230</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>46230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>46276</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>46269</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>46279</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>46281</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>46238</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>46238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>46283</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>46286</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>46283</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>46287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44825</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>46282</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>46288</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>46288</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>46288</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45971</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>46007</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45713</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>46244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>46244</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>46289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>46080</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46294</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>46294</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46294</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46296</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46251</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>46254</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45919</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>46093</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>46297</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>46006</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>46258</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>46301</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>46304</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>46304</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>44379</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45194</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45427</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45418</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45117</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>44991</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45119</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45425</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>44519</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45440</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45583</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>44519</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45119</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45105</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45122</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>44479</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>46010</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>46018</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>46050</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>46052</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45483</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44546</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46030</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44508</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45772</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45209</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45335</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46078</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>46195</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46268</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46286</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>46287</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>43980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>45418</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>44602</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>44629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44853</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44788</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44557</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44608</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44852</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44480</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44515</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44848</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44502</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44525</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44606</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44776</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44616</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44706</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44539</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>44760</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>44776</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>44496</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>44662</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>44678</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44648</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45406</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>45343</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>45343</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8602,7 +8602,7 @@
         <v>45642</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45078</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45037</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45372</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45363</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45208</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45208</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45763</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45267</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44823</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45105</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45105</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45105</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45496</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44727</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45221</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45162</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45021</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>45302</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44998</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>44853</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44853</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45756</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45393</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45243</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45200</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45558</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45315</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45245</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45446</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45056</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45401</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44539</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45371</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45547</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>44494</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44882</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44949</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45278</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45505</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45271</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45149</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44966</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45785</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44805</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45853</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45853</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45576</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45618</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45512</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>44936</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45713</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45687</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45583</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45589</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45483</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45271</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45019</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45674</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44602</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13981,7 +13981,7 @@
         <v>45889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45894</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>44981</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45667</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45204</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45758</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44984</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45597</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45531</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45229</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>45475</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45194</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45358</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45029</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45146</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45106</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44970</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45264</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45562</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45091</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45667</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45124</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45769</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45777</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45553</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45264</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45264</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45589</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45428</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45357</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45670</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45203</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45915</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45445</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44949</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45250</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45547</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45917</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44559</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45468</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45517</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45524</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45243</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44998</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44998</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44595</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45790</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>44553</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>44553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45924</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45217</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45561</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>44890</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45713</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45567</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>45188</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44642</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44642</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45723</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45261</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45197</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45197</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45567</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45160</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45558</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45796</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45631</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45721</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45792</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>44566</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45635</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45558</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45328</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45328</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45674</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45204</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45371</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45587</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45587</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45800</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45439</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45645</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>45684</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45142</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45803</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45372</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45554</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44956</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45044</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44608</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45608</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45642</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45772</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45180</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45670</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45607</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45946</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>44699</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45649</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45270</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45819</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44698</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45820</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44931</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45173</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45826</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44929</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44942</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44526</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45188</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>45832</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44722</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45637</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45012</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45769</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45957</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45957</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45957</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45659</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45805</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45274</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45833</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44678</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45258</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45194</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45414</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45688</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45965</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45965</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45674</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45967</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44851</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>45278</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45841</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45701</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45238</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45841</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45841</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45971</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45674</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45845</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>44729</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45243</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>44686</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45586</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45604</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44909</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45853</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45189</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45748</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45328</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45265</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45272</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45320</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>44722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45219</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45161</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44797</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45802</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>44859</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28087,7 +28087,7 @@
         <v>44846</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45873</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28306,7 +28306,7 @@
         <v>45191</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44727</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45224</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45275</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45873</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>45876</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45278</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45279</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45981</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45200</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44820</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45154</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45267</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45509</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45509</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45566</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>46099</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>46099</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45735</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45610</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>45986</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45986</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45701</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45302</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44936</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>45446</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>46105</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45072</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45308</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45308</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44993</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45987</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45735</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45987</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45590</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45989</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45394</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45069</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44869</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>46101</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45993</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>46127</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44652</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>46001</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>46001</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44840</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45443</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>46006</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>44985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>44928</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46003</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45566</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44970</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45607</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45200</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45187</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45203</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45873</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45957</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45841</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45905</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45308</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45036</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45734</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45876</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45726</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>44501</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>44846</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45043</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>44616</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45758</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46029</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>46030</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45245</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46139</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45245</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45221</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>46034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44971</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>46034</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45509</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45642</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>44903</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44642</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45106</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45274</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45812</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>45966</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>46037</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>46038</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>46038</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46038</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46042</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46042</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45112</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45841</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45912</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>46045</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45567</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45386</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45519</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45357</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45563</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45917</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>46045</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46045</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45400</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>46050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>45827</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>46049</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45664</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>46057</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>46057</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>46062</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>46062</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>46064</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38211,7 +38211,7 @@
         <v>46064</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46066</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46073</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46073</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>46073</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46073</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>44831</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46073</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46079</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>46080</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45718</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46086</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46160</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>46092</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46093</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46167</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46167</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46167</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46167</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46172</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45945</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45972</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46183</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46182</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>46184</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46185</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>46189</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>46188</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46188</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>46188</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46188</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>46188</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>46191</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46191</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46190</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46191</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>46191</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46191</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>46195</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46195</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46195</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41770,7 +41770,7 @@
         <v>46195</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>46193</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>46195</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46195</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>46195</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46206</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>46206</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>46206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46206</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45924</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46105</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>46265</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46265</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46265</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45728</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>46267</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46268</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>46230</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>46230</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>46230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>46276</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>46269</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>46279</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>46281</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>46238</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>46238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>46283</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>46286</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>46283</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>46287</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44825</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>46282</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>46288</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>46288</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>46288</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46288</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45971</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>46288</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>46007</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>46098</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45713</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>46244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>46244</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45193,7 +45193,7 @@
         <v>46289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>46080</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46294</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>46294</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46294</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46296</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>46251</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>46254</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45919</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>46093</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>46297</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>46006</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>46258</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>46301</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>46304</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>46304</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>44379</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45194</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45427</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45418</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45117</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>44991</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45119</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45425</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>44519</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45440</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45583</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>44519</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45119</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45105</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45122</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>44479</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>46010</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>46018</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>46050</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>46052</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44546</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45483</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45772</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45209</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45335</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45091</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46286</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>46287</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46307</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>45841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45418</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>46260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44628</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44788</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44760</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44776</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44848</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44496</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44616</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44662</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44648</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>45597</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45328</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45166</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45642</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45358</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44869</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45394</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45238</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45772</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45142</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45315</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45250</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44595</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45769</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>44909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45363</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45558</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45558</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45328</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45483</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45761</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45553</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45200</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45187</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44859</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45208</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45019</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44678</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45524</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45245</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45221</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44903</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44846</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45446</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45637</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44602</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45587</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44577</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45610</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44566</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44727</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45069</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45590</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45267</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45371</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45203</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45667</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44840</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45562</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45519</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45853</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45217</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45328</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45957</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45758</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45583</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45324</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44722</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45576</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45670</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45264</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45091</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45889</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45853</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45567</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45889</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45785</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45873</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45905</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44853</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44853</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45894</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45678</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45785</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44722</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45512</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45936</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45807</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45758</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45664</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45509</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45876</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45827</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45509</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45175</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45566</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45642</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44823</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45208</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45124</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>44966</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>45274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45229</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45684</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45239</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45320</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45959</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45261</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44993</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45718</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45957</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45957</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44882</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45965</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45112</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45667</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45966</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45967</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46160</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45971</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45372</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45972</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45400</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45221</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46162</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45642</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44970</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45975</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45975</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45369</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>44998</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44608</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45986</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>46167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45446</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45357</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45756</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45993</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45993</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46167</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45995</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45496</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>46167</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45264</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44985</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>45021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>46003</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>46001</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>46001</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45401</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>44557</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45278</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45972</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45687</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44928</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45607</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45308</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>46172</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45558</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45622</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>44970</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45734</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45200</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45106</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44686</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>44942</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45414</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>46030</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46030</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46037</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46038</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>46177</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>46038</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44797</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45302</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>46042</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>46042</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45589</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>46042</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46045</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>46044</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46045</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46045</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46049</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45505</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45267</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45264</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45007</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>46182</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>46057</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>46057</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>46183</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45443</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>46062</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46064</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>46064</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44652</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>46066</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45072</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45271</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45162</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>46188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46188</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46073</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46073</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46073</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>46073</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46073</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46073</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>46188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45769</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45204</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45475</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46079</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45474</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46189</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46086</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46190</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46190</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>46092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46193</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46191</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46191</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46191</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46195</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45509</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>46099</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>46195</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46099</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45308</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>46195</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46195</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45105</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45105</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46105</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46105</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45631</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45012</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>46195</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46101</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45357</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44846</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45517</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45713</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>44526</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46127</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45371</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46127</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45238</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45160</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45219</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45223</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45912</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>46206</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44501</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45114</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45674</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45674</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46206</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45563</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44587</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45243</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45243</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44559</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45278</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45728</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45200</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45170</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45093</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46230</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45372</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45406</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46279</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45596</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45194</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>44729</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44949</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45270</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44890</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45105</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45674</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45009</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45688</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45554</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46281</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45721</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45547</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>46238</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>46238</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>45245</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>44949</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45243</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>44553</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44553</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45701</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45971</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45393</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46282</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45173</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45343</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>45343</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45167</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>46289</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45566</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>44805</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>46288</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>44698</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46288</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46288</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>44825</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45713</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46007</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46080</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45044</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45278</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46244</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45607</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>46294</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>46294</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45279</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44699</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>46294</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46251</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45197</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45271</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45265</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>46254</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44998</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>44998</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46297</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>46006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45036</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46301</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>46093</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>46258</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45777</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45589</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>45919</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>45468</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45428</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45547</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45243</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45445</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45790</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45723</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45561</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45792</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46307</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45796</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46265</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>46265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>46307</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45674</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46304</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46304</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45803</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46308</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45800</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45439</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>46308</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>46309</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>46265</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46308</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45180</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>46308</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45670</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45608</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45649</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45819</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45820</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46269</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>46310</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45825</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45825</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46268</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45826</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46267</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45832</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45832</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45833</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45659</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>45841</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45841</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>45841</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45845</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45586</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45604</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45853</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45802</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45873</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45873</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45876</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44379</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45194</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45427</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45418</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45117</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>44991</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45425</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>44519</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45440</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45583</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>44519</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45119</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45105</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45122</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>46010</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46018</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>44546</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>46030</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45483</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45205</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45772</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45209</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45335</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46078</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46195</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45091</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46286</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>46287</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>46307</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>45841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45418</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>46260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44566</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44628</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44788</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44753</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44600</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44760</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44776</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44848</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44496</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44616</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44662</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44648</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44929</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>45597</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44727</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45328</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45618</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>45567</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45567</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>45166</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45735</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45642</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44616</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45358</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44869</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45394</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45238</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45772</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45142</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45315</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45250</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44595</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45635</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>45769</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>45267</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>44909</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>45363</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>45735</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45558</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45558</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>45328</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>45483</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45761</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>45553</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45200</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45308</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45187</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44859</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44981</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45208</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45019</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44678</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45531</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45524</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45245</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>45221</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44903</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44846</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45446</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>45203</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>45189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>44642</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>44642</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44956</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45637</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>44602</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45587</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45587</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44577</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45610</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44566</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44727</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45069</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45590</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45267</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45371</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45203</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45667</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44840</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45562</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45519</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45853</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45217</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45328</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45726</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45957</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45758</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45245</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45583</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45324</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>44722</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45576</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>45917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45670</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45264</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>45091</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45889</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45853</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45567</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45889</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45785</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>44494</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45873</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45905</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44853</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44853</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45894</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45678</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45785</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>44722</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45512</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45936</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>45807</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45812</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45758</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45664</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>45509</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44984</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45876</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45827</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45509</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45175</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45566</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45642</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44823</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45208</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45917</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45124</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45924</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>44966</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>45274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45229</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45149</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45684</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45946</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45239</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45320</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>45959</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45261</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44993</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45718</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45957</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>45957</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44882</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45965</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45112</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>45667</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45966</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45713</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45967</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46160</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45971</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45043</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45971</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45372</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45972</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45400</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45221</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46162</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45642</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44970</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45975</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45975</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45272</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45369</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>44998</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44608</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45986</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45987</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>46167</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45986</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45446</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45357</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45756</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>45989</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45993</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45993</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46167</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>45763</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45995</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45496</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>46167</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45264</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>44985</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>45021</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>46003</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>46001</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>46001</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45401</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>44557</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45278</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46006</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44539</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45972</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45687</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>44928</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45607</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45308</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>46172</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45608</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45558</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45622</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>44970</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45734</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45200</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45106</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44686</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>44942</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45414</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>46030</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46030</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45274</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>46034</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46037</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46038</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>46177</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>46038</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>44797</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45302</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>46042</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>46042</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>45589</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         <v>46042</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46045</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>46044</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45701</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46045</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46045</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46049</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>45505</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45267</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45264</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45007</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>46182</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>46057</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>46057</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>46183</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45443</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45106</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>46062</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>46185</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>46064</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>46064</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44652</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>46066</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45072</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>45271</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>46188</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45162</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>46188</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>46188</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46073</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>46073</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46073</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>46073</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46073</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46073</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>46188</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45769</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45204</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45475</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46079</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45474</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>46189</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46086</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46190</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46190</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>46092</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46193</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46191</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46191</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46191</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46191</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46195</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>46195</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45509</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>46099</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>46195</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>46099</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>45308</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>46195</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>46195</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>46195</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45105</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45105</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46105</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46105</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45631</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45012</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>46195</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46101</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45357</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45069</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44846</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45517</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45713</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>44526</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>46127</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45371</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46127</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45238</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45160</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45219</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45223</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45912</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>46206</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44501</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45924</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>46206</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45114</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45674</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45674</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46206</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45563</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44587</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45243</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45243</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44559</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45278</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45728</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45200</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44820</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45170</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46230</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45093</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46230</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45372</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45645</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45406</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45275</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46279</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45596</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45194</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>44729</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44949</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45270</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44890</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45105</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45674</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45009</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45688</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45554</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46281</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45721</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45547</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>46238</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>46238</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>45245</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>44949</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>45243</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45558</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>44553</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44553</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45701</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45971</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46287</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45393</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46282</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45173</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45343</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>45343</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>46286</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45188</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45167</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>46289</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45566</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>44805</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>46288</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>46288</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46288</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>46288</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>44698</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>46288</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>46288</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>44825</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45713</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46007</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>44936</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>46080</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45044</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46244</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45278</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46244</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45607</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>46294</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>46294</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45279</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44699</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>46294</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46251</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45197</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>46294</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45146</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45271</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45265</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>46254</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>44998</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>44998</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46297</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>46296</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>46006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45036</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46301</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>46093</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>46258</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45037</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45777</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45589</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>45919</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>45468</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45428</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45547</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45243</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45445</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>45790</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45723</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45561</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45792</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46307</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45796</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46265</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>46265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>46307</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45674</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>46304</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>46304</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45803</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>46308</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>46283</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         <v>45800</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45439</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>46308</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>46309</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>46265</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46308</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45180</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>46308</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45670</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45608</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45649</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45819</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45820</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46269</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>46310</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45825</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45825</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46268</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>45826</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46267</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45832</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45832</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45833</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45805</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45659</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>45841</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45841</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>45841</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45845</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45586</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45604</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45853</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45802</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>45873</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45873</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45876</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44379</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45194</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45427</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45418</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45117</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>44991</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45119</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45425</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>44519</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45440</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45583</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>44519</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45119</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45105</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45122</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>46010</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46018</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>46030</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45205</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45483</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44546</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>46195</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45539</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>46287</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>46307</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45772</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45264</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45418</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>46260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>44566</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44788</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44760</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44776</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44848</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44496</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44616</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44662</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45566</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44648</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45785</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45576</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44970</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45607</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45200</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45763</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45512</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45267</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44823</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45889</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45221</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45174</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45894</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45187</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45324</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45401</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45758</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45807</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45194</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44501</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45406</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45267</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46160</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45343</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44616</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>46162</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45245</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45245</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45221</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>44971</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45474</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44903</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44642</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44577</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45274</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>46167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45175</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45112</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46167</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>46167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>46167</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>46172</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45037</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45972</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45369</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45386</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45357</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45563</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45363</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45400</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45302</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44853</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44853</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45756</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45393</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45372</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45243</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45558</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45315</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>46177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45243</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45009</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45328</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45105</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45105</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45105</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>46183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45678</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45957</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45957</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46182</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45957</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44998</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45105</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46185</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45200</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>46189</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>46188</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>46188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>46191</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>46190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45056</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45967</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>46191</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>46190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>46190</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46195</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46195</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45971</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>46193</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46195</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>46195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46195</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45371</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45596</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45547</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44882</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45278</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45505</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45167</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45618</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45713</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45981</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45687</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45986</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>46204</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45674</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>46206</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45987</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>46206</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45924</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45667</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45204</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45597</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45229</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45989</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>45358</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45684</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45993</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45993</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45146</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45264</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45667</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>46001</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45777</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>46003</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45589</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45428</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>46230</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>46230</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46230</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45445</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>46279</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45547</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45468</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44949</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45308</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45271</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45790</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45734</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46281</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46238</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>46238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>46029</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46030</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46030</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45561</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>46034</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46034</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45723</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>46283</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45796</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46037</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46286</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>46038</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>46038</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46038</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46287</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>46042</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45792</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>46288</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>46044</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44825</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46288</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>46288</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46288</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45674</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46045</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46288</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46007</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>46098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45800</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46049</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45439</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44966</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45803</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45713</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46289</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45608</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46080</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46057</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>46057</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45180</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>46062</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>46064</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46294</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>46294</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>46064</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46066</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45819</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45820</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46073</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46296</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46073</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46073</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>46073</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>46073</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46251</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46073</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45825</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46079</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45832</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45659</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45805</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45832</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46086</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45833</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>46254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45919</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46092</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46093</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>46093</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46099</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46006</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45841</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45845</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44602</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>46258</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45586</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>46301</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45604</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46105</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44981</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44984</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45531</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45475</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46304</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46101</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45802</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45873</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45873</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45876</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46308</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46307</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46308</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45069</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45562</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45113</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46307</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45357</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46283</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45670</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45203</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44557</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46308</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44949</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>46309</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46308</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44943</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46310</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45558</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45873</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45957</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45905</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45876</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45726</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45524</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44998</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44998</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45758</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46268</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44587</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44595</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46139</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45007</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>44553</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44553</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45509</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45812</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45217</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46269</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44890</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45567</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45936</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45966</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45261</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45197</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45197</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45912</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45567</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45558</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45567</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45519</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45889</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45917</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46317</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46276</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45827</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45558</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45664</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45587</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45587</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45142</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>44956</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44994</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45772</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45093</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>44831</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45718</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>45270</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44931</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44929</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44942</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44526</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45044</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44722</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45637</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45012</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45414</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45166</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>45674</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45701</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45674</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44722</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>45219</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45161</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>44797</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>44846</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45036</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45191</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>44727</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45224</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45200</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45154</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45509</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45761</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45735</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45446</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45072</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45735</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45069</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44869</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45208</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45208</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45496</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45021</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>44887</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45238</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45149</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>44805</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>44936</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45589</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45019</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>45029</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45106</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>44970</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45114</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45124</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45769</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45553</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45264</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45264</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45162</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45250</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45167</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44559</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45517</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45188</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44642</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>44642</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45160</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45631</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45721</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45608</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44566</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45635</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45328</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45328</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45371</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45645</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45684</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45372</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45554</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45044</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44608</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45642</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45607</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44698</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45093</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45173</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44678</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45194</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45688</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45239</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>44851</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45278</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45238</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44729</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45243</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44686</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>44909</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45328</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45320</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45275</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45278</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44820</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45509</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45566</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45610</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45701</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45302</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44936</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45223</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45308</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45308</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>44993</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45590</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45394</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>44652</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44840</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45443</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44985</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44379</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45194</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45427</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45418</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45117</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>44991</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>45425</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>44519</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45440</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45583</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>44519</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45119</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45105</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45122</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46010</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46018</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>46052</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt VÄRNAMO.xlsx
+++ b/Översikt VÄRNAMO.xlsx
@@ -601,7 +601,7 @@
         <v>46018</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         <v>46160</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46267</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45070</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45119</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45048</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>45327</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>46030</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45205</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45483</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44546</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44879</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45070</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45712</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45825</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>46000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45091</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45766</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>46195</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>45539</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>46287</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>46078</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>46307</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46268</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45772</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45076</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45264</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>45209</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>43980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45418</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>46260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44602</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>44566</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44628</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>44629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44788</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44608</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44770</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44854</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44607</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44629</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44496</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44539</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44760</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44776</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44848</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44776</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44496</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44557</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44606</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44616</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44706</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44662</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45566</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44648</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45785</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>45853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>45576</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44970</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45607</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45200</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45763</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45512</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45583</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45267</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44823</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45889</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45221</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45174</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45894</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45187</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45324</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45203</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45401</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45758</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45807</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45194</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44501</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45406</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45267</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44846</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45043</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46160</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45343</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44616</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>46162</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45245</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45245</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45221</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>44971</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45474</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44903</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44642</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>44577</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45274</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45917</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>46167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45175</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>45112</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46167</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>46167</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>46167</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>46172</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>45037</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>45972</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45369</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45386</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45357</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45563</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45363</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45400</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45078</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45302</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>44853</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>44853</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45756</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45393</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45372</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45243</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45946</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45558</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45315</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>46177</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45243</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45009</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45328</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45105</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45105</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45105</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44727</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>46183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45678</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45957</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45957</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>46182</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45162</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>45957</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>44998</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45105</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45105</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>46184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46185</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45200</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>46189</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>46188</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>46188</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>46188</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>45966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45965</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>46188</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>46188</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>46191</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>46191</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>46190</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45056</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46191</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45967</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>46191</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>46191</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>46190</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>46190</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>46195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45971</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>46195</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46195</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>46195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45971</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46195</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>46193</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>46195</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>46195</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>46195</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45371</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45596</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45972</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45547</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44882</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45278</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45505</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45167</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45618</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45713</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45981</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45687</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45271</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45986</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>46204</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45674</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>46206</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45987</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>46206</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45924</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45667</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45204</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>45597</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45229</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45989</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>45358</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45684</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45993</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45993</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45146</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45264</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45667</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>46001</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45777</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>46003</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45589</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45428</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>46230</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>46230</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>46230</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45445</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44494</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>46279</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>46279</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45547</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45468</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44949</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45308</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45243</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45271</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45790</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45734</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46281</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46238</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23494,7 +23494,7 @@
         <v>46238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>46029</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46030</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46030</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45561</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>46034</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46034</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45723</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>46283</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45796</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46037</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>46286</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>46038</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>46038</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46038</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>46042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46287</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>46042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>46042</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45792</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>46288</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>46044</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44825</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>46282</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46288</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>46288</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>46288</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45674</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46045</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46288</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45971</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46050</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46007</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>46098</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45800</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46049</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45439</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44966</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45803</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45713</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46244</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46289</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45608</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46080</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46057</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>46057</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45180</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>46062</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>46062</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>46064</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46294</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>46294</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>46064</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>46294</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>46294</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46066</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45819</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>45820</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46073</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46296</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>46073</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46073</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>46073</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>46073</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46251</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46073</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45825</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45825</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46079</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45826</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45832</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45659</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45805</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45832</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46086</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>45833</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45170</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>46254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45919</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46092</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46093</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>46093</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46099</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45841</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46006</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46099</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45841</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45841</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45845</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44602</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>46258</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45586</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>46301</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45604</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>46105</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46105</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44981</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45853</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45748</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44984</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45531</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45475</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46304</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>46304</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46101</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45802</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45873</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45873</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45876</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46308</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46307</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46308</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45069</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45562</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>45113</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46307</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45357</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46283</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45670</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45203</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45785</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44557</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46308</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44949</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>46309</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>46308</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44943</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>46310</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45558</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>45873</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45957</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45905</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45876</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>45726</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45524</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44998</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44998</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45758</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46268</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44587</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>44595</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>46139</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45007</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>44553</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>44553</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45509</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>45812</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45217</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>46269</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44890</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45567</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>45936</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45966</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45261</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45197</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>45197</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>45912</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>45567</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>45558</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45567</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>45519</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45889</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45917</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46317</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>46276</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45827</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45558</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45664</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45587</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45587</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>45142</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>44956</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44994</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45772</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45093</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>44831</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>45718</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>45270</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>44931</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44929</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44942</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44526</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45044</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44722</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45637</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45012</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45414</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>45166</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>45674</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45701</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45674</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45189</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44722</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>45219</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45161</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>44797</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>44846</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45036</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45191</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39490,7 +39490,7 @@
         <v>44727</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45224</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45200</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45154</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45267</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45509</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45761</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45735</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45446</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45072</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45735</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45069</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44869</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45208</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45208</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45496</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45021</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45245</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>44887</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45238</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>45149</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>44805</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>44936</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>45589</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45019</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>45029</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45106</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>44970</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>45114</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45124</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>45769</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45553</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45264</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45264</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45162</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45250</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>45167</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44559</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45517</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45713</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45188</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44642</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>44642</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45160</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45631</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>45721</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45608</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>44566</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>45635</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45328</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45328</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45371</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45645</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45684</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45372</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45554</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45044</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>44608</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45642</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45607</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>44699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>44698</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45093</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45173</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44678</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45194</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45688</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45239</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>44851</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45278</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45238</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44729</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45243</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45239,7 +45239,7 @@
         <v>44686</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>44909</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45328</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45320</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44859</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45275</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45278</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45279</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44820</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45509</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45566</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45610</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45701</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45302</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44936</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45223</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45308</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45308</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>44993</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45590</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>45394</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>44652</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44840</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45443</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44985</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>44379</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45194</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45427</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45418</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45117</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>44991</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45119</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47746,7 +47746,7 @@
         <v>45425</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>44519</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45440</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45583</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>44519</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45119</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45105</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45122</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46010</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>46018</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>46052</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
